--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Money 2025" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$36</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -781,6 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BF36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -884,7 +885,7 @@
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
     </row>
-    <row r="2" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>0</v>
       </c>
@@ -962,7 +963,7 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
     </row>
-    <row r="3" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>0</v>
       </c>
@@ -1040,7 +1041,7 @@
       <c r="BE3" s="1"/>
       <c r="BF3" s="1"/>
     </row>
-    <row r="4" spans="1:58" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1115,7 +1116,7 @@
       <c r="BE4" s="1"/>
       <c r="BF4" s="1"/>
     </row>
-    <row r="5" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1192,7 +1193,7 @@
       <c r="BE5" s="1"/>
       <c r="BF5" s="1"/>
     </row>
-    <row r="6" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1367,7 +1368,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="3">
-        <v>1700115743</v>
+        <v>401172574</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
@@ -1435,7 +1436,7 @@
       <c r="BE8" s="1"/>
       <c r="BF8" s="1"/>
     </row>
-    <row r="9" spans="1:58" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" s="3" customFormat="1" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1514,7 +1515,7 @@
       <c r="BE9" s="1"/>
       <c r="BF9" s="1"/>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1547,7 +1548,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -1628,7 +1629,7 @@
       <c r="BE11" s="1"/>
       <c r="BF11" s="1"/>
     </row>
-    <row r="12" spans="1:58" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -1780,7 +1781,7 @@
       </c>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>13</v>
       </c>
@@ -1844,7 +1845,7 @@
       </c>
       <c r="L16" s="21"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -1878,7 +1879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -1978,7 +1979,7 @@
       </c>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -2040,7 +2041,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -2072,7 +2073,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -2102,7 +2103,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -2132,7 +2133,7 @@
       <c r="K25" s="11"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -2164,7 +2165,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -2229,7 +2230,7 @@
       <c r="K28" s="11"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -2259,7 +2260,7 @@
       <c r="K29" s="11"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -2289,7 +2290,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -2379,7 +2380,7 @@
       <c r="K33" s="11"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -2409,7 +2410,7 @@
       <c r="K34" s="11"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -2439,7 +2440,7 @@
       <c r="K35" s="11"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -2470,7 +2471,13 @@
       <c r="L36" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C32"/>
+  <autoFilter ref="C1:C36">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Ouled Djellal"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -261,7 +261,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ _€"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,6 +303,13 @@
       <b/>
       <sz val="14"/>
       <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -373,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -500,6 +507,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -781,7 +794,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:BF36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -885,7 +897,7 @@
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
     </row>
-    <row r="2" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>0</v>
       </c>
@@ -963,7 +975,7 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
     </row>
-    <row r="3" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>0</v>
       </c>
@@ -1041,7 +1053,7 @@
       <c r="BE3" s="1"/>
       <c r="BF3" s="1"/>
     </row>
-    <row r="4" spans="1:58" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:58" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1116,7 +1128,7 @@
       <c r="BE4" s="1"/>
       <c r="BF4" s="1"/>
     </row>
-    <row r="5" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1193,7 +1205,7 @@
       <c r="BE5" s="1"/>
       <c r="BF5" s="1"/>
     </row>
-    <row r="6" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -1436,7 +1448,7 @@
       <c r="BE8" s="1"/>
       <c r="BF8" s="1"/>
     </row>
-    <row r="9" spans="1:58" s="3" customFormat="1" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:58" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1515,7 +1527,7 @@
       <c r="BE9" s="1"/>
       <c r="BF9" s="1"/>
     </row>
-    <row r="10" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1548,7 +1560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:58" s="3" customFormat="1" ht="37.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -1629,7 +1641,7 @@
       <c r="BE11" s="1"/>
       <c r="BF11" s="1"/>
     </row>
-    <row r="12" spans="1:58" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:58" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -1781,7 +1793,7 @@
       </c>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -1813,7 +1825,7 @@
       </c>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:58" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>13</v>
       </c>
@@ -1845,7 +1857,7 @@
       </c>
       <c r="L16" s="21"/>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -1879,7 +1891,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -1913,7 +1925,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -1979,7 +1991,7 @@
       </c>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -2011,7 +2023,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -2041,7 +2053,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -2073,7 +2085,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -2103,7 +2115,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -2133,7 +2145,7 @@
       <c r="K25" s="11"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -2165,7 +2177,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -2200,7 +2212,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -2230,7 +2242,7 @@
       <c r="K28" s="11"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -2260,7 +2272,7 @@
       <c r="K29" s="11"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -2290,7 +2302,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -2380,7 +2392,7 @@
       <c r="K33" s="11"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -2410,7 +2422,7 @@
       <c r="K34" s="11"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -2440,7 +2452,7 @@
       <c r="K35" s="11"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -2471,13 +2483,7 @@
       <c r="L36" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C36">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Ouled Djellal"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="C1:C36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3440,17 +3446,17 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="28">
+      <c r="A2" s="43">
         <v>2</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="26">
-        <v>10000</v>
+      <c r="D2" s="44">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -3753,7 +3759,7 @@
       <c r="C24" s="32"/>
       <c r="D24" s="33">
         <f>SUM(D1:D23)</f>
-        <v>620000</v>
+        <v>610000</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -3784,7 +3790,7 @@
       <c r="C28" s="42"/>
       <c r="D28" s="29">
         <f>D26+D24</f>
-        <v>730000</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -3863,7 +3869,7 @@
       <c r="C42" s="42"/>
       <c r="D42" s="29">
         <f>SUM(D3:D40)</f>
-        <v>2120000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
@@ -3884,7 +3890,7 @@
       <c r="C46" s="42"/>
       <c r="D46" s="29">
         <f>D42-D44</f>
-        <v>2110000</v>
+        <v>2090000</v>
       </c>
     </row>
   </sheetData>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="74">
   <si>
     <t>Direction</t>
   </si>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t>equipementt3</t>
+  </si>
+  <si>
+    <t>Logmatrix99</t>
   </si>
 </sst>
 </file>
@@ -380,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -505,13 +508,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2684,7 +2690,25 @@
       <c r="BF2" s="1"/>
     </row>
     <row r="3" spans="1:58" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="45">
+        <v>1605916027</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="H3" s="4"/>
+      <c r="I3" s="9">
+        <v>46464</v>
+      </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -3379,32 +3403,32 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="29">
         <f>SUM(D1:D14)</f>
         <v>600000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
       <c r="D18" s="27">
         <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="29">
         <f>D16-D18</f>
         <v>590000</v>
@@ -3446,16 +3470,16 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="42">
         <v>2</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3783,11 +3807,11 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
       <c r="D28" s="29">
         <f>D26+D24</f>
         <v>720000</v>
@@ -3862,32 +3886,32 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="42" t="s">
+      <c r="A42" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
       <c r="D42" s="29">
         <f>SUM(D3:D40)</f>
         <v>2100000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="42" t="s">
+      <c r="A44" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
       <c r="D44" s="27">
         <v>10000</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="42" t="s">
+      <c r="A46" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
       <c r="D46" s="29">
         <f>D42-D44</f>
         <v>2090000</v>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -311,8 +311,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
-      <color theme="5"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -383,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -451,9 +452,6 @@
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -508,16 +506,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,7 +799,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF36"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -1236,7 +1234,7 @@
       <c r="H6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="29">
         <v>46326</v>
       </c>
       <c r="J6" s="9"/>
@@ -1316,7 +1314,7 @@
       <c r="H7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="29">
         <v>46326</v>
       </c>
       <c r="J7" s="16">
@@ -1398,7 +1396,7 @@
         <v>19</v>
       </c>
       <c r="H8" s="4"/>
-      <c r="I8" s="30">
+      <c r="I8" s="29">
         <v>46326</v>
       </c>
       <c r="J8" s="9">
@@ -1477,7 +1475,7 @@
         <v>19</v>
       </c>
       <c r="H9" s="8"/>
-      <c r="I9" s="30">
+      <c r="I9" s="29">
         <v>46326</v>
       </c>
       <c r="K9" s="9">
@@ -1556,7 +1554,7 @@
         <v>19</v>
       </c>
       <c r="H10" s="4"/>
-      <c r="I10" s="30">
+      <c r="I10" s="29">
         <v>46326</v>
       </c>
       <c r="K10" s="9">
@@ -1591,7 +1589,7 @@
       <c r="H11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="29">
         <v>46326</v>
       </c>
       <c r="K11" s="9">
@@ -1669,7 +1667,7 @@
       <c r="G12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="24">
         <v>45961</v>
       </c>
       <c r="K12" s="9"/>
@@ -1748,7 +1746,7 @@
         <v>19</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="30">
+      <c r="I13" s="29">
         <v>46326</v>
       </c>
       <c r="J13" s="9">
@@ -1788,7 +1786,7 @@
         <v>19</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="I14" s="25">
+      <c r="I14" s="24">
         <v>45961</v>
       </c>
       <c r="J14" s="9">
@@ -1822,7 +1820,7 @@
         <v>19</v>
       </c>
       <c r="H15" s="4"/>
-      <c r="I15" s="31">
+      <c r="I15" s="30">
         <v>46326</v>
       </c>
       <c r="J15" s="3"/>
@@ -1854,11 +1852,11 @@
         <v>19</v>
       </c>
       <c r="H16" s="22"/>
-      <c r="I16" s="23">
-        <v>45961</v>
+      <c r="I16" s="30">
+        <v>46326</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="K16" s="24">
+      <c r="K16" s="23">
         <v>45475</v>
       </c>
       <c r="L16" s="21"/>
@@ -1886,7 +1884,7 @@
         <v>19</v>
       </c>
       <c r="H17" s="4"/>
-      <c r="I17" s="31">
+      <c r="I17" s="30">
         <v>46326</v>
       </c>
       <c r="J17" s="3"/>
@@ -1920,7 +1918,7 @@
         <v>19</v>
       </c>
       <c r="H18" s="4"/>
-      <c r="I18" s="31">
+      <c r="I18" s="30">
         <v>46326</v>
       </c>
       <c r="J18" s="3"/>
@@ -1986,7 +1984,7 @@
         <v>19</v>
       </c>
       <c r="H20" s="4"/>
-      <c r="I20" s="31">
+      <c r="I20" s="30">
         <v>46326</v>
       </c>
       <c r="J20" s="9">
@@ -2020,7 +2018,7 @@
         <v>19</v>
       </c>
       <c r="H21" s="4"/>
-      <c r="I21" s="31">
+      <c r="I21" s="30">
         <v>46326</v>
       </c>
       <c r="J21" s="3"/>
@@ -2082,7 +2080,7 @@
         <v>19</v>
       </c>
       <c r="H23" s="4"/>
-      <c r="I23" s="31">
+      <c r="I23" s="30">
         <v>46326</v>
       </c>
       <c r="J23" s="3"/>
@@ -2114,7 +2112,7 @@
         <v>19</v>
       </c>
       <c r="H24" s="4"/>
-      <c r="I24" s="31">
+      <c r="I24" s="30">
         <v>46326</v>
       </c>
       <c r="J24" s="3"/>
@@ -2144,7 +2142,7 @@
         <v>19</v>
       </c>
       <c r="H25" s="4"/>
-      <c r="I25" s="31">
+      <c r="I25" s="30">
         <v>46326</v>
       </c>
       <c r="J25" s="3"/>
@@ -2498,7 +2496,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -2693,7 +2691,7 @@
       <c r="C3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="41">
         <v>1605916027</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -3136,7 +3134,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -3227,7 +3225,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3244,7 +3242,7 @@
       <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="26">
+      <c r="D1" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3258,7 +3256,7 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3272,21 +3270,21 @@
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="25">
         <v>50000</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>4</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3300,7 +3298,7 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3314,7 +3312,7 @@
       <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3328,7 +3326,7 @@
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3342,7 +3340,7 @@
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3356,7 +3354,7 @@
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3370,7 +3368,7 @@
       <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3384,7 +3382,7 @@
       <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3398,38 +3396,38 @@
       <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="26">
         <v>50000</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="29">
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="28">
         <f>SUM(D1:D14)</f>
         <v>600000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="27">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="29">
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="28">
         <f>D16-D18</f>
         <v>590000</v>
       </c>
@@ -3448,7 +3446,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3456,30 +3454,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="39">
+      <c r="A1" s="38">
         <v>1</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="40">
+      <c r="D1" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="42">
+      <c r="A2" s="43">
         <v>2</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="44">
         <v>0</v>
       </c>
     </row>
@@ -3493,7 +3491,7 @@
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="25">
         <v>10000</v>
       </c>
     </row>
@@ -3507,7 +3505,7 @@
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="25">
         <v>10000</v>
       </c>
     </row>
@@ -3521,7 +3519,7 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="25">
         <v>10000</v>
       </c>
     </row>
@@ -3535,7 +3533,7 @@
       <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="25">
         <v>10000</v>
       </c>
     </row>
@@ -3549,7 +3547,7 @@
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="25">
         <v>10000</v>
       </c>
     </row>
@@ -3563,21 +3561,21 @@
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>10000</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="37">
+      <c r="A9" s="36">
         <v>9</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="37">
         <v>0</v>
       </c>
     </row>
@@ -3591,21 +3589,21 @@
       <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="25">
         <v>10000</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="37">
+      <c r="A11" s="36">
         <v>11</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="37">
         <v>0</v>
       </c>
     </row>
@@ -3619,7 +3617,7 @@
       <c r="C12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3633,7 +3631,7 @@
       <c r="C13" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="33">
         <v>20000</v>
       </c>
     </row>
@@ -3641,13 +3639,13 @@
       <c r="A14" s="3">
         <v>14</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="35" t="s">
+      <c r="C14" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="35">
         <v>70000</v>
       </c>
     </row>
@@ -3661,7 +3659,7 @@
       <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3675,7 +3673,7 @@
       <c r="C16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3689,7 +3687,7 @@
       <c r="C17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3703,7 +3701,7 @@
       <c r="C18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3717,7 +3715,7 @@
       <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3731,7 +3729,7 @@
       <c r="C20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3745,7 +3743,7 @@
       <c r="C21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3759,7 +3757,7 @@
       <c r="C22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="25">
         <v>50000</v>
       </c>
     </row>
@@ -3767,30 +3765,30 @@
       <c r="A23" s="3">
         <v>23</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33">
+      <c r="A24" s="31"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32">
         <f>SUM(D1:D23)</f>
         <v>610000</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="33"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="32"/>
     </row>
     <row r="26" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
@@ -3799,77 +3797,77 @@
       <c r="B26" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="26">
         <v>110000</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="29">
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="28">
         <f>D26+D24</f>
         <v>720000</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="33"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="32"/>
     </row>
     <row r="30" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="33"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="32"/>
     </row>
     <row r="31" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="33"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
     </row>
     <row r="32" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="33"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="32"/>
     </row>
     <row r="33" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="33"/>
+      <c r="A33" s="31"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="32"/>
     </row>
     <row r="34" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="33"/>
+      <c r="A34" s="31"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="32"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="33"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="32"/>
     </row>
     <row r="36" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="33"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="32"/>
     </row>
     <row r="37" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="33"/>
+      <c r="A37" s="31"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="32"/>
     </row>
     <row r="40" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
@@ -3881,38 +3879,38 @@
       <c r="C40" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="26">
         <v>50000</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="44" t="s">
+      <c r="A42" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="44"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="29">
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="28">
         <f>SUM(D3:D40)</f>
         <v>2100000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="44" t="s">
+      <c r="A44" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="27">
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="29">
+      <c r="B46" s="42"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="28">
         <f>D42-D44</f>
         <v>2090000</v>
       </c>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="74">
   <si>
     <t>Direction</t>
   </si>
@@ -509,14 +509,14 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF36"/>
+  <dimension ref="A1:BF37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2486,6 +2486,34 @@
       <c r="K36" s="11"/>
       <c r="L36" s="3"/>
     </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="21">
+        <v>34</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="21">
+        <v>1761783449</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21">
+        <v>46326</v>
+      </c>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+    </row>
   </sheetData>
   <autoFilter ref="C1:C36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3401,32 +3429,32 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
       <c r="D16" s="28">
         <f>SUM(D1:D14)</f>
         <v>600000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
       <c r="D18" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
       <c r="D20" s="28">
         <f>D16-D18</f>
         <v>590000</v>
@@ -3468,16 +3496,16 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="42">
         <v>2</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="43">
         <v>0</v>
       </c>
     </row>
@@ -3805,11 +3833,11 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
       <c r="D28" s="28">
         <f>D26+D24</f>
         <v>720000</v>
@@ -3884,32 +3912,32 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="42" t="s">
+      <c r="A42" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
       <c r="D42" s="28">
         <f>SUM(D3:D40)</f>
         <v>2100000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="42" t="s">
+      <c r="A44" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
       <c r="D44" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="42" t="s">
+      <c r="A46" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
       <c r="D46" s="28">
         <f>D42-D44</f>
         <v>2090000</v>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="74">
   <si>
     <t>Direction</t>
   </si>
@@ -798,8 +798,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BF38"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -2514,6 +2514,14 @@
       <c r="K37" s="21"/>
       <c r="L37" s="21"/>
     </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D38" s="1">
+        <v>449344618</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="C1:C36"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2524,7 +2532,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -3162,7 +3170,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -3253,7 +3261,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3474,7 +3482,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="74">
   <si>
     <t>Direction</t>
   </si>
@@ -799,7 +799,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF38"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -2515,6 +2515,15 @@
       <c r="L37" s="21"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D38" s="1">
         <v>449344618</v>
       </c>
@@ -2532,7 +2541,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -3170,7 +3179,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -3261,7 +3270,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3482,7 +3491,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Money 2025" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$38</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="74">
   <si>
     <t>Direction</t>
   </si>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="G37" s="21"/>
       <c r="H37" s="21"/>
-      <c r="I37" s="21">
+      <c r="I37" s="23">
         <v>46326</v>
       </c>
       <c r="J37" s="21"/>
@@ -2515,24 +2515,37 @@
       <c r="L37" s="21"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="A38" s="3">
         <v>35</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="3">
         <v>449344618</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="F38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="9">
+        <v>46326</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C36"/>
+  <autoFilter ref="C1:C38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -384,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -517,6 +517,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -799,7 +814,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -1058,33 +1073,34 @@
       <c r="BF3" s="1"/>
     </row>
     <row r="4" spans="1:58" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="36">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="36">
         <v>1139732168</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="9">
+      <c r="I4" s="18">
         <v>45596</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="36"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -1133,35 +1149,36 @@
       <c r="BF4" s="1"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="36">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="36">
         <v>1495102636</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="18">
         <v>45596</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="10"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="36"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -1930,36 +1947,36 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="A19" s="38">
         <v>16</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="38">
         <v>401804188</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="18">
+      <c r="H19" s="47"/>
+      <c r="I19" s="48">
         <v>45961</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="9">
+      <c r="J19" s="38"/>
+      <c r="K19" s="48">
         <v>45501</v>
       </c>
-      <c r="L19" s="3"/>
+      <c r="L19" s="38"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -2028,34 +2045,34 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="A22" s="36">
         <v>19</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="36">
         <v>1195041370</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="45"/>
       <c r="I22" s="18">
         <v>45961</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="3"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="36"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
@@ -2397,29 +2414,29 @@
       <c r="L33" s="3"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="A34" s="36">
         <v>31</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="36">
         <v>1544086645</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="9">
+      <c r="H34" s="45"/>
+      <c r="I34" s="18">
         <v>46326</v>
       </c>
       <c r="J34" s="3"/>
@@ -2554,7 +2571,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -3192,7 +3209,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -3283,7 +3300,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3504,7 +3521,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -515,23 +515,23 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1099,7 +1099,7 @@
         <v>45596</v>
       </c>
       <c r="J4" s="18"/>
-      <c r="K4" s="46"/>
+      <c r="K4" s="45"/>
       <c r="L4" s="36"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -1149,36 +1149,35 @@
       <c r="BF4" s="1"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="36">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="3">
         <v>1495102636</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="18">
-        <v>45596</v>
-      </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="36"/>
+      <c r="I5" s="29">
+        <v>46326</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -1968,12 +1967,12 @@
       <c r="G19" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="47"/>
-      <c r="I19" s="48">
+      <c r="H19" s="46"/>
+      <c r="I19" s="47">
         <v>45961</v>
       </c>
       <c r="J19" s="38"/>
-      <c r="K19" s="48">
+      <c r="K19" s="47">
         <v>45501</v>
       </c>
       <c r="L19" s="38"/>
@@ -2066,12 +2065,12 @@
       <c r="G22" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="45"/>
+      <c r="H22" s="44"/>
       <c r="I22" s="18">
         <v>45961</v>
       </c>
       <c r="J22" s="36"/>
-      <c r="K22" s="49"/>
+      <c r="K22" s="48"/>
       <c r="L22" s="36"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -2435,7 +2434,7 @@
       <c r="G34" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H34" s="45"/>
+      <c r="H34" s="44"/>
       <c r="I34" s="18">
         <v>46326</v>
       </c>
@@ -3476,32 +3475,32 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="28">
         <f>SUM(D1:D14)</f>
         <v>600000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
       <c r="D18" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
       <c r="D20" s="28">
         <f>D16-D18</f>
         <v>590000</v>
@@ -3880,11 +3879,11 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="28">
         <f>D26+D24</f>
         <v>720000</v>
@@ -3959,32 +3958,32 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="44" t="s">
+      <c r="A42" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="44"/>
-      <c r="C42" s="44"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
       <c r="D42" s="28">
         <f>SUM(D3:D40)</f>
         <v>2100000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="44" t="s">
+      <c r="A44" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
       <c r="D44" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
       <c r="D46" s="28">
         <f>D42-D44</f>
         <v>2090000</v>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="74">
   <si>
     <t>Direction</t>
   </si>
@@ -2521,7 +2521,9 @@
       <c r="F37" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="G37" s="21"/>
+      <c r="G37" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="H37" s="21"/>
       <c r="I37" s="23">
         <v>46326</v>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -1591,7 +1591,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="3">
-        <v>1198616846</v>
+        <v>1104600811</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>6</v>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="75">
   <si>
     <t>Direction</t>
   </si>
@@ -255,6 +255,9 @@
   </si>
   <si>
     <t>Logmatrix99</t>
+  </si>
+  <si>
+    <t>10.30.0.18</t>
   </si>
 </sst>
 </file>
@@ -1591,10 +1594,10 @@
         <v>25</v>
       </c>
       <c r="D11" s="3">
-        <v>1104600811</v>
+        <v>1735686024</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>16</v>
@@ -1612,7 +1615,7 @@
         <v>45501</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
